--- a/astro-site/public/dl/seafood-restaurant-checklist-templates/01-seafood-restaurant-opening-closing-checklist.xlsx
+++ b/astro-site/public/dl/seafood-restaurant-checklist-templates/01-seafood-restaurant-opening-closing-checklist.xlsx
@@ -848,7 +848,7 @@
       <c r="E14" s="6" t="inlineStr"/>
       <c r="F14" s="6" t="inlineStr"/>
     </row>
-    <row r="15" ht="20" customHeight="1">
+    <row r="15" ht="54.5" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Walk-ins</t>
@@ -856,7 +856,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Check the live shellfish walk-in temperature (varies by species)</t>
+          <t>Check the live shellfish walk-in temperature: shellstock at 41 °F or below once received (FDA Food Code 3-202.11); live crustaceans per your supplier — log reading: ____ °F</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -896,7 +896,7 @@
       <c r="E16" s="6" t="inlineStr"/>
       <c r="F16" s="6" t="inlineStr"/>
     </row>
-    <row r="17" ht="20" customHeight="1">
+    <row r="17" ht="68" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
           <t>Kitchen</t>
@@ -904,23 +904,23 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Mise en place sauces: cocktail sauce, mignonette, tartar, remoulade, drawn butter</t>
+          <t>Thaw scheduled products (FIFO, lot log): in the walk-in at 41 °F or below or under cold running water at 70 °F or below (FDA Food Code 3-501.13); take vacuum-packed (ROP) frozen fish out of the bag when thawing</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Sauce station</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>8:00 AM</t>
+          <t>7:30 AM</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr"/>
       <c r="F17" s="6" t="inlineStr"/>
     </row>
-    <row r="18" ht="20" customHeight="1">
+    <row r="18" ht="33.25" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Kitchen</t>
@@ -928,12 +928,12 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Make today's fish stock / fumet</t>
+          <t>Mise en place sauces: cocktail sauce, mignonette, tartar, remoulade, drawn butter</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Stock station</t>
+          <t>Sauce station</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -952,23 +952,23 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Check side stock: potatoes, peppers, greens</t>
+          <t>Make today's fish stock / fumet</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Stock station</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>8:30 AM</t>
+          <t>8:00 AM</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr"/>
       <c r="F19" s="6" t="inlineStr"/>
     </row>
-    <row r="20" ht="33.25" customHeight="1">
+    <row r="20" ht="20" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
           <t>Kitchen</t>
@@ -976,12 +976,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Set up mise en place for the flat-top griddle / grill</t>
+          <t>Check side stock: potatoes, peppers, greens</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Grill cook</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -992,7 +992,7 @@
       <c r="E20" s="6" t="inlineStr"/>
       <c r="F20" s="6" t="inlineStr"/>
     </row>
-    <row r="21" ht="68" customHeight="1">
+    <row r="21" ht="20" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
           <t>Kitchen</t>
@@ -1000,17 +1000,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Thaw scheduled products (FIFO, lot log): in the walk-in at 41 °F or below or under cold running water at 70 °F or below (FDA Food Code 3-501.13); take vacuum-packed (ROP) frozen fish out of the bag when thawing</t>
+          <t>Set up mise en place for the flat-top griddle / grill</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Grill cook</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>7:30 AM</t>
+          <t>8:30 AM</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr"/>
@@ -1211,22 +1211,22 @@
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>FOH</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Fish / shellfish inventory: stock left vs. tomorrow's order</t>
+          <t>Collect the seafood service tools, wash and store them</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Head chef</t>
+          <t>FOH</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>11:15 PM</t>
+          <t>11:00 PM</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr"/>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Log today's waste (high-value product)</t>
+          <t>Fish / shellfish inventory: stock left vs. tomorrow's order</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
@@ -1256,7 +1256,7 @@
       <c r="E32" s="6" t="inlineStr"/>
       <c r="F32" s="6" t="inlineStr"/>
     </row>
-    <row r="33" ht="41" customHeight="1">
+    <row r="33" ht="20" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
         <is>
           <t>Kitchen</t>
@@ -1264,23 +1264,23 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Deep clean the fish area and cutting boards, then sanitize at label strength, checked with test strips (FDA Food Code 4-501.114)</t>
+          <t>Log today's waste (high-value product)</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Head chef</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>11:30 PM</t>
+          <t>11:15 PM</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr"/>
       <c r="F33" s="6" t="inlineStr"/>
     </row>
-    <row r="34" ht="20" customHeight="1">
+    <row r="34" ht="41" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
         <is>
           <t>Kitchen</t>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Check walk-ins: temperature and doors closed</t>
+          <t>Deep clean the fish area and cutting boards, then sanitize at label strength, checked with test strips (FDA Food Code 4-501.114)</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
@@ -1307,22 +1307,22 @@
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>FOH</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Collect the seafood service tools, wash and store them</t>
+          <t>Check walk-ins: temperature and doors closed</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>FOH</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>11:00 PM</t>
+          <t>11:30 PM</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr"/>
